--- a/data/trans_orig/P57C2_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P57C2_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se ha sentido bien consigo mismo/a en 2023</t>
+          <t>Población según si se ha sentido bien consigo mismo/a en 2023 (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2140</t>
+          <t>2238</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16466</t>
+          <t>15515</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>758</t>
+          <t>592</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6062</t>
+          <t>6279</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4255</t>
+          <t>4341</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20256</t>
+          <t>19007</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5863</t>
+          <t>5978</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19514</t>
+          <t>18788</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4362</t>
+          <t>4119</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15662</t>
+          <t>15140</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12567</t>
+          <t>12161</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>29605</t>
+          <t>29339</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19150</t>
+          <t>19668</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>42149</t>
+          <t>42001</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14912</t>
+          <t>14958</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>29086</t>
+          <t>30704</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>37949</t>
+          <t>38700</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>64733</t>
+          <t>65185</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,84%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>211118</t>
+          <t>209969</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>255918</t>
+          <t>257353</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>41,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>50,66%</t>
+          <t>50,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>186456</t>
+          <t>186787</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>222732</t>
+          <t>224817</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>41,67%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>49,78%</t>
+          <t>50,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>405769</t>
+          <t>409035</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>468936</t>
+          <t>467954</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>49,22%</t>
+          <t>49,12%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>200585</t>
+          <t>200928</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>247389</t>
+          <t>248329</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>48,97%</t>
+          <t>49,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>191063</t>
+          <t>193179</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>229637</t>
+          <t>229127</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>43,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>51,32%</t>
+          <t>51,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>405859</t>
+          <t>407268</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>466543</t>
+          <t>464263</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>48,97%</t>
+          <t>48,73%</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>4180</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>628</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5980</t>
+          <t>5063</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7324</t>
+          <t>7201</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,86%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3371</t>
+          <t>3506</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20789</t>
+          <t>21980</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4282</t>
+          <t>4929</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13659</t>
+          <t>14640</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>10263</t>
+          <t>10497</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>29519</t>
+          <t>28611</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15586</t>
+          <t>14785</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>33160</t>
+          <t>32142</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>22847</t>
+          <t>23704</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>42001</t>
+          <t>42125</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>42042</t>
+          <t>43392</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>68484</t>
+          <t>68258</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,18%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>185319</t>
+          <t>183995</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>227833</t>
+          <t>225414</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>40,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>50,38%</t>
+          <t>49,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>174572</t>
+          <t>174223</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>206985</t>
+          <t>207158</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>45,63%</t>
+          <t>45,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>54,1%</t>
+          <t>54,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>368110</t>
+          <t>367092</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>422517</t>
+          <t>423393</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>43,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,61%</t>
+          <t>50,72%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>193245</t>
+          <t>194626</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>235384</t>
+          <t>237062</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>43,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>52,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>133751</t>
+          <t>132872</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>164352</t>
+          <t>165992</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>34,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>43,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>338539</t>
+          <t>335335</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>395656</t>
+          <t>391841</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>47,4%</t>
+          <t>46,94%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>858</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14283</t>
+          <t>14651</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4538</t>
+          <t>4249</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1415</t>
+          <t>1545</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15654</t>
+          <t>16008</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3932</t>
+          <t>4153</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25358</t>
+          <t>25206</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3245</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10342</t>
+          <t>10729</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5409</t>
+          <t>5592</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>30576</t>
+          <t>30697</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11502</t>
+          <t>13196</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>58932</t>
+          <t>62093</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>15662</t>
+          <t>15658</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>28550</t>
+          <t>29201</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>22978</t>
+          <t>24693</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>84666</t>
+          <t>85173</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,2%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>77204</t>
+          <t>87325</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>332842</t>
+          <t>336002</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>49,81%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>73011</t>
+          <t>72399</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>92604</t>
+          <t>93865</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>43,38%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>55,48%</t>
+          <t>56,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>120555</t>
+          <t>127252</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>417165</t>
+          <t>413921</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>49,95%</t>
+          <t>49,56%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>252744</t>
+          <t>247681</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>574327</t>
+          <t>560213</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>83,83%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>45762</t>
+          <t>45250</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>65595</t>
+          <t>66653</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>39,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>302951</t>
+          <t>303337</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>680653</t>
+          <t>667281</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>36,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>79,9%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7851</t>
+          <t>7694</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>22922</t>
+          <t>22570</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3240</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14911</t>
+          <t>15084</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>12735</t>
+          <t>12721</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>31779</t>
+          <t>32870</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>23073</t>
+          <t>22281</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>45332</t>
+          <t>43545</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>15253</t>
+          <t>13783</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>41357</t>
+          <t>41239</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>41640</t>
+          <t>42742</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>78239</t>
+          <t>77889</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>83029</t>
+          <t>83082</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>121290</t>
+          <t>122387</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>34783</t>
+          <t>30689</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>86096</t>
+          <t>84427</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>112935</t>
+          <t>120932</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>192571</t>
+          <t>196219</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,77%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>463044</t>
+          <t>467033</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>534929</t>
+          <t>537208</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>45,2%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>51,77%</t>
+          <t>51,99%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>491968</t>
+          <t>493826</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>770578</t>
+          <t>775560</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>50,45%</t>
+          <t>50,64%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>79,53%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>982980</t>
+          <t>983756</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1364951</t>
+          <t>1356504</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>48,94%</t>
+          <t>48,98%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>67,96%</t>
+          <t>67,54%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>355882</t>
+          <t>351632</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>422845</t>
+          <t>420504</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>148723</t>
+          <t>151752</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>358407</t>
+          <t>356262</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>464568</t>
+          <t>456750</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>750597</t>
+          <t>750444</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>37,36%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5374</t>
+          <t>5169</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>18171</t>
+          <t>17741</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>12329</t>
+          <t>12838</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>31952</t>
+          <t>32381</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>21073</t>
+          <t>20093</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>43468</t>
+          <t>45186</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>17174</t>
+          <t>16050</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>34379</t>
+          <t>34632</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>37857</t>
+          <t>37652</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>65819</t>
+          <t>66946</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>60817</t>
+          <t>59745</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>93423</t>
+          <t>93247</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,1%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>50937</t>
+          <t>52188</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>79296</t>
+          <t>82846</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>82725</t>
+          <t>83065</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>133243</t>
+          <t>133520</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>144727</t>
+          <t>145380</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>202507</t>
+          <t>204810</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,59%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>194908</t>
+          <t>194702</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>241670</t>
+          <t>241390</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>41,07%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>50,98%</t>
+          <t>50,92%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>280534</t>
+          <t>289537</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>433766</t>
+          <t>438408</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>51,64%</t>
+          <t>52,2%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>501161</t>
+          <t>494858</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>659527</t>
+          <t>657923</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>37,66%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>50,19%</t>
+          <t>50,07%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>135084</t>
+          <t>132600</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>180233</t>
+          <t>178345</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>37,62%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>213762</t>
+          <t>212177</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>426735</t>
+          <t>434228</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>50,81%</t>
+          <t>51,7%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>364623</t>
+          <t>368368</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>575471</t>
+          <t>597177</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>45,45%</t>
         </is>
       </c>
     </row>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>5030</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4175,12 +4175,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>6587</t>
+          <t>5991</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>20306</t>
+          <t>19837</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>7733</t>
+          <t>6937</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>20966</t>
+          <t>20770</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>8936</t>
+          <t>7312</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>27412</t>
+          <t>26941</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>44345</t>
+          <t>44984</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>28518</t>
+          <t>27934</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>47130</t>
+          <t>46401</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,65%</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>6028</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>21498</t>
+          <t>22354</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>113473</t>
+          <t>112875</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>149141</t>
+          <t>147414</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4436,12 +4436,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>120174</t>
+          <t>123378</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>163758</t>
+          <t>164350</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,47%</t>
         </is>
       </c>
     </row>
@@ -4479,12 +4479,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>65820</t>
+          <t>68069</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>118058</t>
+          <t>121535</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>49,09%</t>
+          <t>50,53%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4514,12 +4514,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>299256</t>
+          <t>300258</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>352562</t>
+          <t>350839</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>39,65%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>46,33%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>382413</t>
+          <t>381273</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>454972</t>
+          <t>454358</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>45,54%</t>
         </is>
       </c>
     </row>
@@ -4592,12 +4592,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>105911</t>
+          <t>104325</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>159689</t>
+          <t>157760</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4607,12 +4607,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>43,38%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>66,4%</t>
+          <t>65,59%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>232609</t>
+          <t>232860</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>282213</t>
+          <t>283389</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>354972</t>
+          <t>350627</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>424803</t>
+          <t>428099</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>42,57%</t>
+          <t>42,9%</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>26437</t>
+          <t>26680</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>54927</t>
+          <t>54823</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>31208</t>
+          <t>32713</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>59423</t>
+          <t>59764</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>66339</t>
+          <t>64012</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>103405</t>
+          <t>103671</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -4935,12 +4935,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>69875</t>
+          <t>69638</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>112872</t>
+          <t>113833</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>114589</t>
+          <t>113029</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>161058</t>
+          <t>160126</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>192966</t>
+          <t>194592</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>259420</t>
+          <t>260446</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>207733</t>
+          <t>210182</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>305166</t>
+          <t>305685</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>309087</t>
+          <t>301825</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>420535</t>
+          <t>422612</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>555122</t>
+          <t>559488</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>704586</t>
+          <t>702592</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,12%</t>
         </is>
       </c>
     </row>
@@ -5161,12 +5161,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1128726</t>
+          <t>1102594</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>1596132</t>
+          <t>1591695</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>47,18%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>1644847</t>
+          <t>1645597</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>2157376</t>
+          <t>2119940</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>46,1%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>59,39%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>2882232</t>
+          <t>2942046</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>3573516</t>
+          <t>3559703</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>41,51%</t>
+          <t>42,38%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>51,27%</t>
         </is>
       </c>
     </row>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1353934</t>
+          <t>1354298</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>1943375</t>
+          <t>1995966</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5289,12 +5289,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>57,61%</t>
+          <t>59,17%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1019052</t>
+          <t>1011469</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>1353213</t>
+          <t>1347228</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>37,74%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>2476387</t>
+          <t>2482542</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>3213358</t>
+          <t>3184816</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>45,87%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P57C2_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P57C2_2023-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>6802</t>
+          <t>7285</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2238</t>
+          <t>2251</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15515</t>
+          <t>17612</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2384</t>
+          <t>2553</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>806</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6279</t>
+          <t>6376</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>9186</t>
+          <t>9838</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4341</t>
+          <t>4370</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19007</t>
+          <t>19656</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11217</t>
+          <t>11516</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5978</t>
+          <t>6369</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18788</t>
+          <t>19632</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8287</t>
+          <t>10869</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4119</t>
+          <t>5866</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15140</t>
+          <t>21097</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>19505</t>
+          <t>22386</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12161</t>
+          <t>14631</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>29339</t>
+          <t>34619</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>29203</t>
+          <t>31492</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19668</t>
+          <t>21716</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>42001</t>
+          <t>44477</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>21142</t>
+          <t>22865</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14958</t>
+          <t>16086</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>30704</t>
+          <t>32218</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>50345</t>
+          <t>54356</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>38700</t>
+          <t>42114</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>65185</t>
+          <t>71923</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,92%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>234172</t>
+          <t>250441</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>209969</t>
+          <t>225542</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>257353</t>
+          <t>277287</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>45,48%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>40,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>50,94%</t>
+          <t>50,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>205687</t>
+          <t>220887</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>186787</t>
+          <t>203198</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>224817</t>
+          <t>241418</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>45,23%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>41,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>50,24%</t>
+          <t>49,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>439859</t>
+          <t>471327</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>409035</t>
+          <t>439188</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>467954</t>
+          <t>499554</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>45,36%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>42,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>49,12%</t>
+          <t>48,08%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>223818</t>
+          <t>249885</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>200928</t>
+          <t>225519</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>248329</t>
+          <t>275060</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>44,3%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>40,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>49,15%</t>
+          <t>49,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>209967</t>
+          <t>231237</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>193179</t>
+          <t>211823</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>229127</t>
+          <t>251369</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>46,92%</t>
+          <t>47,34%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>43,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>51,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>433785</t>
+          <t>481122</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>407268</t>
+          <t>452646</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>464263</t>
+          <t>512718</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>45,53%</t>
+          <t>46,3%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>43,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>48,73%</t>
+          <t>49,35%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1248</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4180</t>
+          <t>5654</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,22 +1442,22 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>2658</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>675</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5063</t>
+          <t>6648</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>3245</t>
+          <t>4171</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1515</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7201</t>
+          <t>9358</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8429</t>
+          <t>8399</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3506</t>
+          <t>3413</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21980</t>
+          <t>18650</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8361</t>
+          <t>9182</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4929</t>
+          <t>4769</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14640</t>
+          <t>15336</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>16790</t>
+          <t>17581</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>10497</t>
+          <t>10858</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>28611</t>
+          <t>29957</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>23253</t>
+          <t>24391</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14785</t>
+          <t>16857</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>32142</t>
+          <t>34698</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>31565</t>
+          <t>34820</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>23704</t>
+          <t>25863</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>42125</t>
+          <t>46221</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>54818</t>
+          <t>59210</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>43392</t>
+          <t>47607</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>68258</t>
+          <t>74386</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,21%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>204614</t>
+          <t>215759</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>183995</t>
+          <t>193094</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>225414</t>
+          <t>237276</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>45,25%</t>
+          <t>44,65%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,85%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>191733</t>
+          <t>206882</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>174223</t>
+          <t>188837</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>207158</t>
+          <t>225771</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>48,89%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>44,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>54,15%</t>
+          <t>53,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>396347</t>
+          <t>422640</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>367092</t>
+          <t>394146</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>423393</t>
+          <t>451092</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>47,48%</t>
+          <t>46,63%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>43,97%</t>
+          <t>43,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,72%</t>
+          <t>49,77%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>214669</t>
+          <t>233150</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>194626</t>
+          <t>210381</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>237062</t>
+          <t>256598</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>47,47%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>43,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>52,42%</t>
+          <t>53,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>148924</t>
+          <t>169603</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>132872</t>
+          <t>151884</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>165992</t>
+          <t>189067</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>40,08%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>44,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>363593</t>
+          <t>402752</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>335335</t>
+          <t>371815</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>391841</t>
+          <t>430633</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>44,44%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>41,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>46,94%</t>
+          <t>47,51%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>5320</t>
+          <t>5178</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>858</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14651</t>
+          <t>13947</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1243</t>
+          <t>1326</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2134,12 +2134,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4249</t>
+          <t>4538</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>6564</t>
+          <t>6504</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1545</t>
+          <t>2477</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16008</t>
+          <t>13995</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>13153</t>
+          <t>13917</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4153</t>
+          <t>8198</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25206</t>
+          <t>21887</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5943</t>
+          <t>6710</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>3369</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10729</t>
+          <t>12521</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>19096</t>
+          <t>20627</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5592</t>
+          <t>14579</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>30697</t>
+          <t>29611</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>35078</t>
+          <t>37405</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>13196</t>
+          <t>27482</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>62093</t>
+          <t>50273</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>21524</t>
+          <t>22889</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>15658</t>
+          <t>16627</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>29201</t>
+          <t>31202</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>56602</t>
+          <t>60294</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>24693</t>
+          <t>47543</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>85173</t>
+          <t>73148</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>11,1%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>205134</t>
+          <t>224924</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>87325</t>
+          <t>202935</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>336002</t>
+          <t>245500</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>47,69%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>43,03%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>50,28%</t>
+          <t>52,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>82835</t>
+          <t>90732</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>72399</t>
+          <t>78715</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>93865</t>
+          <t>102652</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>49,63%</t>
+          <t>48,39%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>41,98%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>56,24%</t>
+          <t>54,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>287969</t>
+          <t>315656</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>127252</t>
+          <t>289697</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>413921</t>
+          <t>341156</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>47,89%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>51,76%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>409578</t>
+          <t>190188</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>247681</t>
+          <t>168479</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>560213</t>
+          <t>212722</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>40,33%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,83%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>55367</t>
+          <t>65839</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>45250</t>
+          <t>54506</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>66653</t>
+          <t>78398</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>41,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>464945</t>
+          <t>256027</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>303337</t>
+          <t>231508</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>667281</t>
+          <t>284106</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>43,1%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>13777</t>
+          <t>15833</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7694</t>
+          <t>8810</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>22570</t>
+          <t>25660</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>7791</t>
+          <t>9817</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>5476</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>15084</t>
+          <t>18221</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>21569</t>
+          <t>25651</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>12721</t>
+          <t>17000</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>32870</t>
+          <t>37348</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>32426</t>
+          <t>35496</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>22281</t>
+          <t>25580</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>43545</t>
+          <t>48728</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>29228</t>
+          <t>31720</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>13783</t>
+          <t>23630</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>41239</t>
+          <t>42287</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>61654</t>
+          <t>67216</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>42742</t>
+          <t>53651</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>77889</t>
+          <t>82392</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>100939</t>
+          <t>109393</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>83082</t>
+          <t>90409</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>122387</t>
+          <t>131066</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>62942</t>
+          <t>72242</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>30689</t>
+          <t>60741</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>84427</t>
+          <t>86554</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>163881</t>
+          <t>181635</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>120932</t>
+          <t>161594</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>196219</t>
+          <t>209385</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>10,53%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>500445</t>
+          <t>543317</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>467033</t>
+          <t>508674</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>537208</t>
+          <t>579746</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>48,07%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>45,01%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>51,29%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>600903</t>
+          <t>436945</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>493826</t>
+          <t>412372</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>775560</t>
+          <t>463629</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>61,62%</t>
+          <t>50,91%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>50,64%</t>
+          <t>48,05%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>54,02%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1101348</t>
+          <t>980262</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>983756</t>
+          <t>936263</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1356504</t>
+          <t>1028435</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>54,84%</t>
+          <t>49,3%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>48,98%</t>
+          <t>47,08%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>67,54%</t>
+          <t>51,72%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>385639</t>
+          <t>426208</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>351632</t>
+          <t>391396</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>420504</t>
+          <t>463381</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>41,0%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>274331</t>
+          <t>307560</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>151752</t>
+          <t>282643</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>356262</t>
+          <t>334527</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>38,98%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>659970</t>
+          <t>733768</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>456750</t>
+          <t>686479</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>750444</t>
+          <t>779448</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>39,2%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1033226</t>
+          <t>1130247</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1033226</t>
+          <t>1130247</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1033226</t>
+          <t>1130247</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>975195</t>
+          <t>858285</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>975195</t>
+          <t>858285</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>975195</t>
+          <t>858285</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>2008421</t>
+          <t>1988532</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2008421</t>
+          <t>1988532</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2008421</t>
+          <t>1988532</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3453,32 +3453,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>10117</t>
+          <t>10978</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5169</t>
+          <t>5946</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>17741</t>
+          <t>20434</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3488,32 +3488,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>19723</t>
+          <t>21253</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>12838</t>
+          <t>14178</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>32381</t>
+          <t>35992</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>29839</t>
+          <t>32231</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>20093</t>
+          <t>23206</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>45186</t>
+          <t>48516</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -3566,32 +3566,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>24384</t>
+          <t>27349</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>16050</t>
+          <t>18780</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>34632</t>
+          <t>38476</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>52112</t>
+          <t>61338</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>37652</t>
+          <t>49321</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>66946</t>
+          <t>74718</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>76496</t>
+          <t>88687</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>59745</t>
+          <t>75412</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>93247</t>
+          <t>106246</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,61%</t>
         </is>
       </c>
     </row>
@@ -3679,32 +3679,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>65470</t>
+          <t>83868</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>52188</t>
+          <t>68912</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>82846</t>
+          <t>103692</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,32 +3714,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>112784</t>
+          <t>127563</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>83065</t>
+          <t>111840</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>133520</t>
+          <t>145255</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>178254</t>
+          <t>211431</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>145380</t>
+          <t>186144</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>204810</t>
+          <t>239029</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>17,12%</t>
         </is>
       </c>
     </row>
@@ -3792,32 +3792,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>218118</t>
+          <t>253741</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>194702</t>
+          <t>230395</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>241390</t>
+          <t>279768</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>44,75%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>40,64%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>50,92%</t>
+          <t>49,34%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,32 +3827,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>380766</t>
+          <t>390736</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>289537</t>
+          <t>367294</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>438408</t>
+          <t>416179</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>45,33%</t>
+          <t>47,11%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>44,28%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>50,18%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>598883</t>
+          <t>644478</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>494858</t>
+          <t>609864</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>657923</t>
+          <t>678514</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>46,15%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>43,67%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>50,07%</t>
+          <t>48,59%</t>
         </is>
       </c>
     </row>
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>155961</t>
+          <t>191040</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>132600</t>
+          <t>166975</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>178345</t>
+          <t>218020</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>274535</t>
+          <t>228524</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>212177</t>
+          <t>207787</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>434228</t>
+          <t>249839</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>430496</t>
+          <t>419564</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>368368</t>
+          <t>387236</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>597177</t>
+          <t>451737</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>30,05%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>32,35%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>474049</t>
+          <t>566976</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>474049</t>
+          <t>566976</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>474049</t>
+          <t>566976</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>839920</t>
+          <t>829414</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>839920</t>
+          <t>829414</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>839920</t>
+          <t>829414</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1313969</t>
+          <t>1396391</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1313969</t>
+          <t>1396391</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1313969</t>
+          <t>1396391</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>1462</t>
+          <t>1475</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -4145,12 +4145,12 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>5407</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4170,32 +4170,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>10920</t>
+          <t>11676</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>5991</t>
+          <t>7117</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>19837</t>
+          <t>20246</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,32 +4205,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>12382</t>
+          <t>13150</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>6937</t>
+          <t>7646</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>20770</t>
+          <t>21355</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -4248,7 +4248,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>1946</t>
+          <t>2031</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -4258,12 +4258,12 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>7312</t>
+          <t>9813</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4283,32 +4283,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>34976</t>
+          <t>39364</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>26941</t>
+          <t>31078</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>44984</t>
+          <t>50229</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,32 +4318,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>36922</t>
+          <t>41395</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>27934</t>
+          <t>31460</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>46401</t>
+          <t>52921</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,91%</t>
         </is>
       </c>
     </row>
@@ -4361,32 +4361,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>11761</t>
+          <t>11653</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>6028</t>
+          <t>5639</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>22354</t>
+          <t>23371</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4396,32 +4396,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>129924</t>
+          <t>141205</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>112875</t>
+          <t>123262</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>147414</t>
+          <t>163849</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,32 +4431,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>141685</t>
+          <t>152858</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>123378</t>
+          <t>132499</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>164350</t>
+          <t>177332</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,46%</t>
         </is>
       </c>
     </row>
@@ -4474,32 +4474,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>92395</t>
+          <t>80945</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>68069</t>
+          <t>59896</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>121535</t>
+          <t>103862</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>50,53%</t>
+          <t>43,78%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4509,32 +4509,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>325657</t>
+          <t>363698</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>300258</t>
+          <t>334470</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>350839</t>
+          <t>391531</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>39,82%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>46,61%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,32 +4544,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>418052</t>
+          <t>444643</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>381273</t>
+          <t>410763</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>454358</t>
+          <t>483169</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>41,9%</t>
+          <t>41,28%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>44,86%</t>
         </is>
       </c>
     </row>
@@ -4587,32 +4587,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>132943</t>
+          <t>141124</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>104325</t>
+          <t>117526</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>157760</t>
+          <t>162430</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>55,28%</t>
+          <t>59,49%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>49,54%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>65,59%</t>
+          <t>68,47%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4622,32 +4622,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>255833</t>
+          <t>283996</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>232860</t>
+          <t>258232</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>283389</t>
+          <t>313462</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,32 +4657,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>388777</t>
+          <t>425120</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>350627</t>
+          <t>387397</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>428099</t>
+          <t>466772</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>39,47%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>43,33%</t>
         </is>
       </c>
     </row>
@@ -4700,17 +4700,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4735,17 +4735,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>757311</t>
+          <t>839939</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>757311</t>
+          <t>839939</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>757311</t>
+          <t>839939</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>997818</t>
+          <t>1077166</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>997818</t>
+          <t>1077166</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>997818</t>
+          <t>1077166</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4817,32 +4817,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>38727</t>
+          <t>42262</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>26680</t>
+          <t>30264</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>54823</t>
+          <t>57439</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4852,32 +4852,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>44057</t>
+          <t>49283</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>32713</t>
+          <t>37329</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>59764</t>
+          <t>64450</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,32 +4887,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>82784</t>
+          <t>91545</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>64012</t>
+          <t>73787</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>103671</t>
+          <t>113162</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -4930,32 +4930,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>91555</t>
+          <t>98709</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>69638</t>
+          <t>81878</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>113833</t>
+          <t>119240</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4965,32 +4965,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>138908</t>
+          <t>159183</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>113029</t>
+          <t>140111</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>160126</t>
+          <t>180014</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,32 +5000,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>230462</t>
+          <t>257892</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>194592</t>
+          <t>228742</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>260446</t>
+          <t>287785</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -5043,32 +5043,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>265703</t>
+          <t>298201</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>210182</t>
+          <t>265732</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>305685</t>
+          <t>334759</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5078,32 +5078,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>379881</t>
+          <t>421584</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>301825</t>
+          <t>390528</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>422612</t>
+          <t>457997</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>645584</t>
+          <t>719785</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>559488</t>
+          <t>674225</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>702592</t>
+          <t>763078</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,8%</t>
         </is>
       </c>
     </row>
@@ -5156,32 +5156,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>1454877</t>
+          <t>1569126</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1102594</t>
+          <t>1507599</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>1591695</t>
+          <t>1631661</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>43,13%</t>
+          <t>45,62%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5191,32 +5191,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>1787581</t>
+          <t>1709880</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>1645597</t>
+          <t>1656643</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>2119940</t>
+          <t>1762109</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>50,08%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>46,1%</t>
+          <t>45,68%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>59,39%</t>
+          <t>48,59%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>3242458</t>
+          <t>3279006</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>2942046</t>
+          <t>3200034</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>3559703</t>
+          <t>3361021</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>46,7%</t>
+          <t>46,4%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>45,28%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>47,56%</t>
         </is>
       </c>
     </row>
@@ -5269,32 +5269,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>1522608</t>
+          <t>1431595</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1354298</t>
+          <t>1368874</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>1995966</t>
+          <t>1495740</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>39,79%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>59,17%</t>
+          <t>43,48%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5304,32 +5304,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>1218958</t>
+          <t>1286759</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1011469</t>
+          <t>1234229</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>1347228</t>
+          <t>1337635</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>2741567</t>
+          <t>2718353</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>2482542</t>
+          <t>2639907</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>3184816</t>
+          <t>2807006</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>38,47%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>39,72%</t>
         </is>
       </c>
     </row>
@@ -5382,17 +5382,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>3373470</t>
+          <t>3439893</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>3373470</t>
+          <t>3439893</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>3373470</t>
+          <t>3439893</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5417,17 +5417,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>3569385</t>
+          <t>3626688</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>3569385</t>
+          <t>3626688</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>3569385</t>
+          <t>3626688</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>6942855</t>
+          <t>7066581</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>6942855</t>
+          <t>7066581</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>6942855</t>
+          <t>7066581</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
